--- a/Excel/Combining or Merging Tables in ETL tool/July report.xlsx
+++ b/Excel/Combining or Merging Tables in ETL tool/July report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\Combining or Merging Tables in ETL tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B157B14-5CAB-4060-9F00-3F8F4A7F1DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F63AEA5-EC78-4F30-8BCF-F2F7037660FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5D75526E-A71A-47E3-ADB0-1F7CD9D217AA}"/>
   </bookViews>
@@ -107,10 +107,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,7 +484,7 @@
       <c r="A2" s="1">
         <v>43282</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2">
@@ -499,7 +498,7 @@
       <c r="A3" s="1">
         <v>43282</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3">
@@ -513,7 +512,7 @@
       <c r="A4" s="1">
         <v>43282</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4">
@@ -527,7 +526,7 @@
       <c r="A5" s="1">
         <v>43282</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5">
@@ -541,7 +540,7 @@
       <c r="A6" s="1">
         <v>43282</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6">
@@ -555,7 +554,7 @@
       <c r="A7" s="1">
         <v>43282</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7">
@@ -569,7 +568,7 @@
       <c r="A8" s="1">
         <v>43282</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8">
@@ -583,7 +582,7 @@
       <c r="A9" s="1">
         <v>43282</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9">
@@ -597,7 +596,7 @@
       <c r="A10" s="1">
         <v>43282</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10">
@@ -611,7 +610,7 @@
       <c r="A11" s="1">
         <v>43282</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11">
@@ -625,7 +624,7 @@
       <c r="A12" s="1">
         <v>43282</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>6</v>
       </c>
       <c r="C12">
@@ -639,7 +638,7 @@
       <c r="A13" s="1">
         <v>43283</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>6</v>
       </c>
       <c r="C13">
@@ -653,7 +652,7 @@
       <c r="A14" s="1">
         <v>43283</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>6</v>
       </c>
       <c r="C14">
@@ -667,7 +666,7 @@
       <c r="A15" s="1">
         <v>43283</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15">
@@ -681,7 +680,7 @@
       <c r="A16" s="1">
         <v>43283</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16">
@@ -695,7 +694,7 @@
       <c r="A17" s="1">
         <v>43283</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17">
@@ -709,7 +708,7 @@
       <c r="A18" s="1">
         <v>43283</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>8</v>
       </c>
       <c r="C18">
@@ -723,7 +722,7 @@
       <c r="A19" s="1">
         <v>43283</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>4</v>
       </c>
       <c r="C19">
@@ -737,7 +736,7 @@
       <c r="A20" s="1">
         <v>43284</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>4</v>
       </c>
       <c r="C20">
@@ -751,7 +750,7 @@
       <c r="A21" s="1">
         <v>43284</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" t="s">
         <v>5</v>
       </c>
       <c r="C21">
@@ -765,7 +764,7 @@
       <c r="A22" s="1">
         <v>43284</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22">
@@ -779,7 +778,7 @@
       <c r="A23" s="1">
         <v>43284</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23">
@@ -793,7 +792,7 @@
       <c r="A24" s="1">
         <v>43284</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="C24">
@@ -807,7 +806,7 @@
       <c r="A25" s="1">
         <v>43284</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25">
@@ -821,7 +820,7 @@
       <c r="A26" s="1">
         <v>43284</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26">
@@ -835,7 +834,7 @@
       <c r="A27" s="1">
         <v>43284</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" t="s">
         <v>7</v>
       </c>
       <c r="C27">
@@ -849,7 +848,7 @@
       <c r="A28" s="1">
         <v>43284</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" t="s">
         <v>7</v>
       </c>
       <c r="C28">
@@ -863,7 +862,7 @@
       <c r="A29" s="1">
         <v>43284</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" t="s">
         <v>4</v>
       </c>
       <c r="C29">
@@ -877,7 +876,7 @@
       <c r="A30" s="1">
         <v>43284</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" t="s">
         <v>6</v>
       </c>
       <c r="C30">
@@ -891,7 +890,7 @@
       <c r="A31" s="1">
         <v>43284</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31">
@@ -905,7 +904,7 @@
       <c r="A32" s="1">
         <v>43284</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" t="s">
         <v>8</v>
       </c>
       <c r="C32">
@@ -919,7 +918,7 @@
       <c r="A33" s="1">
         <v>43285</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" t="s">
         <v>6</v>
       </c>
       <c r="C33">
@@ -933,7 +932,7 @@
       <c r="A34" s="1">
         <v>43285</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" t="s">
         <v>7</v>
       </c>
       <c r="C34">
@@ -947,7 +946,7 @@
       <c r="A35" s="1">
         <v>43285</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" t="s">
         <v>5</v>
       </c>
       <c r="C35">
@@ -961,7 +960,7 @@
       <c r="A36" s="1">
         <v>43285</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" t="s">
         <v>5</v>
       </c>
       <c r="C36">
@@ -975,7 +974,7 @@
       <c r="A37" s="1">
         <v>43285</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" t="s">
         <v>6</v>
       </c>
       <c r="C37">
@@ -989,7 +988,7 @@
       <c r="A38" s="1">
         <v>43285</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" t="s">
         <v>4</v>
       </c>
       <c r="C38">
@@ -1003,7 +1002,7 @@
       <c r="A39" s="1">
         <v>43285</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" t="s">
         <v>4</v>
       </c>
       <c r="C39">
@@ -1017,7 +1016,7 @@
       <c r="A40" s="1">
         <v>43285</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" t="s">
         <v>4</v>
       </c>
       <c r="C40">
@@ -1031,7 +1030,7 @@
       <c r="A41" s="1">
         <v>43285</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" t="s">
         <v>4</v>
       </c>
       <c r="C41">
@@ -1045,7 +1044,7 @@
       <c r="A42" s="1">
         <v>43286</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" t="s">
         <v>8</v>
       </c>
       <c r="C42">
@@ -1059,7 +1058,7 @@
       <c r="A43" s="1">
         <v>43286</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" t="s">
         <v>8</v>
       </c>
       <c r="C43">
@@ -1073,7 +1072,7 @@
       <c r="A44" s="1">
         <v>43286</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" t="s">
         <v>5</v>
       </c>
       <c r="C44">
@@ -1087,7 +1086,7 @@
       <c r="A45" s="1">
         <v>43286</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" t="s">
         <v>7</v>
       </c>
       <c r="C45">
@@ -1101,7 +1100,7 @@
       <c r="A46" s="1">
         <v>43286</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" t="s">
         <v>6</v>
       </c>
       <c r="C46">
@@ -1115,7 +1114,7 @@
       <c r="A47" s="1">
         <v>43286</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" t="s">
         <v>4</v>
       </c>
       <c r="C47">
@@ -1129,7 +1128,7 @@
       <c r="A48" s="1">
         <v>43286</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" t="s">
         <v>7</v>
       </c>
       <c r="C48">
@@ -1143,7 +1142,7 @@
       <c r="A49" s="1">
         <v>43286</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" t="s">
         <v>6</v>
       </c>
       <c r="C49">
@@ -1157,7 +1156,7 @@
       <c r="A50" s="1">
         <v>43287</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" t="s">
         <v>8</v>
       </c>
       <c r="C50">
@@ -1171,7 +1170,7 @@
       <c r="A51" s="1">
         <v>43287</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" t="s">
         <v>6</v>
       </c>
       <c r="C51">
@@ -1185,7 +1184,7 @@
       <c r="A52" s="1">
         <v>43287</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" t="s">
         <v>4</v>
       </c>
       <c r="C52">
@@ -1199,7 +1198,7 @@
       <c r="A53" s="1">
         <v>43287</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" t="s">
         <v>5</v>
       </c>
       <c r="C53">
@@ -1213,7 +1212,7 @@
       <c r="A54" s="1">
         <v>43287</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" t="s">
         <v>7</v>
       </c>
       <c r="C54">
@@ -1227,7 +1226,7 @@
       <c r="A55" s="1">
         <v>43287</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" t="s">
         <v>4</v>
       </c>
       <c r="C55">
@@ -1241,7 +1240,7 @@
       <c r="A56" s="1">
         <v>43287</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" t="s">
         <v>7</v>
       </c>
       <c r="C56">
@@ -1255,7 +1254,7 @@
       <c r="A57" s="1">
         <v>43287</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" t="s">
         <v>4</v>
       </c>
       <c r="C57">
@@ -1269,7 +1268,7 @@
       <c r="A58" s="1">
         <v>43287</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" t="s">
         <v>6</v>
       </c>
       <c r="C58">
@@ -1283,7 +1282,7 @@
       <c r="A59" s="1">
         <v>43287</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" t="s">
         <v>5</v>
       </c>
       <c r="C59">
@@ -1297,7 +1296,7 @@
       <c r="A60" s="1">
         <v>43287</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" t="s">
         <v>6</v>
       </c>
       <c r="C60">
@@ -1311,7 +1310,7 @@
       <c r="A61" s="1">
         <v>43287</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" t="s">
         <v>4</v>
       </c>
       <c r="C61">
@@ -1325,7 +1324,7 @@
       <c r="A62" s="1">
         <v>43287</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" t="s">
         <v>6</v>
       </c>
       <c r="C62">
@@ -1339,7 +1338,7 @@
       <c r="A63" s="1">
         <v>43287</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" t="s">
         <v>8</v>
       </c>
       <c r="C63">
@@ -1353,7 +1352,7 @@
       <c r="A64" s="1">
         <v>43287</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" t="s">
         <v>4</v>
       </c>
       <c r="C64">
@@ -1367,7 +1366,7 @@
       <c r="A65" s="1">
         <v>43288</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" t="s">
         <v>4</v>
       </c>
       <c r="C65">
@@ -1381,7 +1380,7 @@
       <c r="A66" s="1">
         <v>43288</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" t="s">
         <v>6</v>
       </c>
       <c r="C66">
@@ -1395,7 +1394,7 @@
       <c r="A67" s="1">
         <v>43288</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" t="s">
         <v>4</v>
       </c>
       <c r="C67">
@@ -1409,7 +1408,7 @@
       <c r="A68" s="1">
         <v>43288</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" t="s">
         <v>6</v>
       </c>
       <c r="C68">
@@ -1423,7 +1422,7 @@
       <c r="A69" s="1">
         <v>43288</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" t="s">
         <v>4</v>
       </c>
       <c r="C69">
@@ -1437,7 +1436,7 @@
       <c r="A70" s="1">
         <v>43288</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" t="s">
         <v>7</v>
       </c>
       <c r="C70">
@@ -1451,7 +1450,7 @@
       <c r="A71" s="1">
         <v>43288</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" t="s">
         <v>6</v>
       </c>
       <c r="C71">
@@ -1465,7 +1464,7 @@
       <c r="A72" s="1">
         <v>43288</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" t="s">
         <v>4</v>
       </c>
       <c r="C72">
@@ -1479,7 +1478,7 @@
       <c r="A73" s="1">
         <v>43288</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" t="s">
         <v>4</v>
       </c>
       <c r="C73">
@@ -1493,7 +1492,7 @@
       <c r="A74" s="1">
         <v>43288</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" t="s">
         <v>4</v>
       </c>
       <c r="C74">
@@ -1507,7 +1506,7 @@
       <c r="A75" s="1">
         <v>43288</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" t="s">
         <v>8</v>
       </c>
       <c r="C75">
@@ -1521,7 +1520,7 @@
       <c r="A76" s="1">
         <v>43288</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" t="s">
         <v>4</v>
       </c>
       <c r="C76">
@@ -1535,7 +1534,7 @@
       <c r="A77" s="1">
         <v>43288</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" t="s">
         <v>5</v>
       </c>
       <c r="C77">
@@ -1549,7 +1548,7 @@
       <c r="A78" s="1">
         <v>43289</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" t="s">
         <v>5</v>
       </c>
       <c r="C78">
@@ -1563,7 +1562,7 @@
       <c r="A79" s="1">
         <v>43289</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" t="s">
         <v>4</v>
       </c>
       <c r="C79">
@@ -1577,7 +1576,7 @@
       <c r="A80" s="1">
         <v>43289</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" t="s">
         <v>4</v>
       </c>
       <c r="C80">
@@ -1591,7 +1590,7 @@
       <c r="A81" s="1">
         <v>43289</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" t="s">
         <v>5</v>
       </c>
       <c r="C81">
@@ -1605,7 +1604,7 @@
       <c r="A82" s="1">
         <v>43289</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" t="s">
         <v>8</v>
       </c>
       <c r="C82">
@@ -1619,7 +1618,7 @@
       <c r="A83" s="1">
         <v>43289</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" t="s">
         <v>4</v>
       </c>
       <c r="C83">
@@ -1633,7 +1632,7 @@
       <c r="A84" s="1">
         <v>43289</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" t="s">
         <v>5</v>
       </c>
       <c r="C84">
@@ -1647,7 +1646,7 @@
       <c r="A85" s="1">
         <v>43289</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" t="s">
         <v>8</v>
       </c>
       <c r="C85">
@@ -1661,7 +1660,7 @@
       <c r="A86" s="1">
         <v>43289</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" t="s">
         <v>7</v>
       </c>
       <c r="C86">
@@ -1675,7 +1674,7 @@
       <c r="A87" s="1">
         <v>43289</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" t="s">
         <v>8</v>
       </c>
       <c r="C87">
@@ -1689,7 +1688,7 @@
       <c r="A88" s="1">
         <v>43289</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" t="s">
         <v>4</v>
       </c>
       <c r="C88">
@@ -1703,7 +1702,7 @@
       <c r="A89" s="1">
         <v>43290</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" t="s">
         <v>5</v>
       </c>
       <c r="C89">
@@ -1717,7 +1716,7 @@
       <c r="A90" s="1">
         <v>43290</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" t="s">
         <v>7</v>
       </c>
       <c r="C90">
@@ -1731,7 +1730,7 @@
       <c r="A91" s="1">
         <v>43290</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" t="s">
         <v>4</v>
       </c>
       <c r="C91">
@@ -1745,7 +1744,7 @@
       <c r="A92" s="1">
         <v>43290</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" t="s">
         <v>4</v>
       </c>
       <c r="C92">
@@ -1759,7 +1758,7 @@
       <c r="A93" s="1">
         <v>43290</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" t="s">
         <v>5</v>
       </c>
       <c r="C93">
@@ -1773,7 +1772,7 @@
       <c r="A94" s="1">
         <v>43290</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" t="s">
         <v>5</v>
       </c>
       <c r="C94">
@@ -1787,7 +1786,7 @@
       <c r="A95" s="1">
         <v>43291</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" t="s">
         <v>8</v>
       </c>
       <c r="C95">
@@ -1801,7 +1800,7 @@
       <c r="A96" s="1">
         <v>43291</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" t="s">
         <v>7</v>
       </c>
       <c r="C96">
@@ -1815,7 +1814,7 @@
       <c r="A97" s="1">
         <v>43291</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" t="s">
         <v>7</v>
       </c>
       <c r="C97">
@@ -1829,7 +1828,7 @@
       <c r="A98" s="1">
         <v>43291</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" t="s">
         <v>4</v>
       </c>
       <c r="C98">
@@ -1843,7 +1842,7 @@
       <c r="A99" s="1">
         <v>43291</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" t="s">
         <v>8</v>
       </c>
       <c r="C99">
@@ -1857,7 +1856,7 @@
       <c r="A100" s="1">
         <v>43291</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" t="s">
         <v>6</v>
       </c>
       <c r="C100">
@@ -1871,7 +1870,7 @@
       <c r="A101" s="1">
         <v>43291</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" t="s">
         <v>4</v>
       </c>
       <c r="C101">
@@ -1885,7 +1884,7 @@
       <c r="A102" s="1">
         <v>43291</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" t="s">
         <v>6</v>
       </c>
       <c r="C102">
@@ -1899,7 +1898,7 @@
       <c r="A103" s="1">
         <v>43291</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B103" t="s">
         <v>8</v>
       </c>
       <c r="C103">
@@ -1913,7 +1912,7 @@
       <c r="A104" s="1">
         <v>43291</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" t="s">
         <v>4</v>
       </c>
       <c r="C104">
@@ -1927,7 +1926,7 @@
       <c r="A105" s="1">
         <v>43291</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" t="s">
         <v>7</v>
       </c>
       <c r="C105">
@@ -1941,7 +1940,7 @@
       <c r="A106" s="1">
         <v>43291</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" t="s">
         <v>8</v>
       </c>
       <c r="C106">
@@ -1955,7 +1954,7 @@
       <c r="A107" s="1">
         <v>43291</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" t="s">
         <v>4</v>
       </c>
       <c r="C107">
@@ -1969,7 +1968,7 @@
       <c r="A108" s="1">
         <v>43291</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" t="s">
         <v>5</v>
       </c>
       <c r="C108">
@@ -1983,7 +1982,7 @@
       <c r="A109" s="1">
         <v>43291</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" t="s">
         <v>8</v>
       </c>
       <c r="C109">
@@ -1997,7 +1996,7 @@
       <c r="A110" s="1">
         <v>43291</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110">
@@ -2011,7 +2010,7 @@
       <c r="A111" s="1">
         <v>43291</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" t="s">
         <v>4</v>
       </c>
       <c r="C111">
@@ -2025,7 +2024,7 @@
       <c r="A112" s="1">
         <v>43291</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" t="s">
         <v>7</v>
       </c>
       <c r="C112">
@@ -2039,7 +2038,7 @@
       <c r="A113" s="1">
         <v>43291</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" t="s">
         <v>8</v>
       </c>
       <c r="C113">
@@ -2053,7 +2052,7 @@
       <c r="A114" s="1">
         <v>43292</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" t="s">
         <v>6</v>
       </c>
       <c r="C114">
@@ -2067,7 +2066,7 @@
       <c r="A115" s="1">
         <v>43292</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" t="s">
         <v>8</v>
       </c>
       <c r="C115">
@@ -2081,7 +2080,7 @@
       <c r="A116" s="1">
         <v>43292</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" t="s">
         <v>6</v>
       </c>
       <c r="C116">
@@ -2095,7 +2094,7 @@
       <c r="A117" s="1">
         <v>43292</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" t="s">
         <v>6</v>
       </c>
       <c r="C117">
@@ -2109,7 +2108,7 @@
       <c r="A118" s="1">
         <v>43292</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" t="s">
         <v>8</v>
       </c>
       <c r="C118">
@@ -2123,7 +2122,7 @@
       <c r="A119" s="1">
         <v>43292</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" t="s">
         <v>4</v>
       </c>
       <c r="C119">
@@ -2137,7 +2136,7 @@
       <c r="A120" s="1">
         <v>43292</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" t="s">
         <v>8</v>
       </c>
       <c r="C120">
@@ -2151,7 +2150,7 @@
       <c r="A121" s="1">
         <v>43293</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" t="s">
         <v>8</v>
       </c>
       <c r="C121">
@@ -2165,7 +2164,7 @@
       <c r="A122" s="1">
         <v>43293</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" t="s">
         <v>4</v>
       </c>
       <c r="C122">
@@ -2179,7 +2178,7 @@
       <c r="A123" s="1">
         <v>43293</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" t="s">
         <v>4</v>
       </c>
       <c r="C123">
@@ -2193,7 +2192,7 @@
       <c r="A124" s="1">
         <v>43293</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" t="s">
         <v>6</v>
       </c>
       <c r="C124">
@@ -2207,7 +2206,7 @@
       <c r="A125" s="1">
         <v>43293</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" t="s">
         <v>5</v>
       </c>
       <c r="C125">
@@ -2221,7 +2220,7 @@
       <c r="A126" s="1">
         <v>43293</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" t="s">
         <v>7</v>
       </c>
       <c r="C126">
@@ -2235,7 +2234,7 @@
       <c r="A127" s="1">
         <v>43293</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" t="s">
         <v>4</v>
       </c>
       <c r="C127">
@@ -2249,7 +2248,7 @@
       <c r="A128" s="1">
         <v>43294</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" t="s">
         <v>6</v>
       </c>
       <c r="C128">
@@ -2263,7 +2262,7 @@
       <c r="A129" s="1">
         <v>43294</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" t="s">
         <v>6</v>
       </c>
       <c r="C129">
@@ -2277,7 +2276,7 @@
       <c r="A130" s="1">
         <v>43294</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" t="s">
         <v>5</v>
       </c>
       <c r="C130">
@@ -2291,7 +2290,7 @@
       <c r="A131" s="1">
         <v>43294</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" t="s">
         <v>8</v>
       </c>
       <c r="C131">
@@ -2305,7 +2304,7 @@
       <c r="A132" s="1">
         <v>43294</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" t="s">
         <v>8</v>
       </c>
       <c r="C132">
@@ -2319,7 +2318,7 @@
       <c r="A133" s="1">
         <v>43294</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" t="s">
         <v>5</v>
       </c>
       <c r="C133">
@@ -2333,7 +2332,7 @@
       <c r="A134" s="1">
         <v>43294</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" t="s">
         <v>8</v>
       </c>
       <c r="C134">
@@ -2347,7 +2346,7 @@
       <c r="A135" s="1">
         <v>43294</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" t="s">
         <v>4</v>
       </c>
       <c r="C135">
@@ -2361,7 +2360,7 @@
       <c r="A136" s="1">
         <v>43294</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" t="s">
         <v>5</v>
       </c>
       <c r="C136">
@@ -2375,7 +2374,7 @@
       <c r="A137" s="1">
         <v>43294</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" t="s">
         <v>5</v>
       </c>
       <c r="C137">
@@ -2389,7 +2388,7 @@
       <c r="A138" s="1">
         <v>43295</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" t="s">
         <v>4</v>
       </c>
       <c r="C138">
@@ -2403,7 +2402,7 @@
       <c r="A139" s="1">
         <v>43295</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" t="s">
         <v>8</v>
       </c>
       <c r="C139">
@@ -2417,7 +2416,7 @@
       <c r="A140" s="1">
         <v>43295</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" t="s">
         <v>6</v>
       </c>
       <c r="C140">
@@ -2431,7 +2430,7 @@
       <c r="A141" s="1">
         <v>43295</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" t="s">
         <v>6</v>
       </c>
       <c r="C141">
@@ -2445,7 +2444,7 @@
       <c r="A142" s="1">
         <v>43295</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" t="s">
         <v>5</v>
       </c>
       <c r="C142">
@@ -2459,7 +2458,7 @@
       <c r="A143" s="1">
         <v>43295</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" t="s">
         <v>4</v>
       </c>
       <c r="C143">
@@ -2473,7 +2472,7 @@
       <c r="A144" s="1">
         <v>43295</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" t="s">
         <v>4</v>
       </c>
       <c r="C144">
@@ -2487,7 +2486,7 @@
       <c r="A145" s="1">
         <v>43295</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" t="s">
         <v>5</v>
       </c>
       <c r="C145">
@@ -2501,7 +2500,7 @@
       <c r="A146" s="1">
         <v>43295</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" t="s">
         <v>7</v>
       </c>
       <c r="C146">
@@ -2515,7 +2514,7 @@
       <c r="A147" s="1">
         <v>43295</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" t="s">
         <v>7</v>
       </c>
       <c r="C147">
@@ -2529,7 +2528,7 @@
       <c r="A148" s="1">
         <v>43295</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B148" t="s">
         <v>5</v>
       </c>
       <c r="C148">
@@ -2543,7 +2542,7 @@
       <c r="A149" s="1">
         <v>43296</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" t="s">
         <v>5</v>
       </c>
       <c r="C149">
@@ -2557,7 +2556,7 @@
       <c r="A150" s="1">
         <v>43296</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" t="s">
         <v>8</v>
       </c>
       <c r="C150">
@@ -2571,7 +2570,7 @@
       <c r="A151" s="1">
         <v>43296</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" t="s">
         <v>5</v>
       </c>
       <c r="C151">
@@ -2585,7 +2584,7 @@
       <c r="A152" s="1">
         <v>43296</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B152" t="s">
         <v>6</v>
       </c>
       <c r="C152">
@@ -2599,7 +2598,7 @@
       <c r="A153" s="1">
         <v>43296</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="B153" t="s">
         <v>7</v>
       </c>
       <c r="C153">
@@ -2613,7 +2612,7 @@
       <c r="A154" s="1">
         <v>43296</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B154" t="s">
         <v>6</v>
       </c>
       <c r="C154">
@@ -2627,7 +2626,7 @@
       <c r="A155" s="1">
         <v>43296</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="B155" t="s">
         <v>7</v>
       </c>
       <c r="C155">
@@ -2641,7 +2640,7 @@
       <c r="A156" s="1">
         <v>43296</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B156" t="s">
         <v>5</v>
       </c>
       <c r="C156">
@@ -2655,7 +2654,7 @@
       <c r="A157" s="1">
         <v>43296</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="B157" t="s">
         <v>4</v>
       </c>
       <c r="C157">
@@ -2669,7 +2668,7 @@
       <c r="A158" s="1">
         <v>43296</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="B158" t="s">
         <v>8</v>
       </c>
       <c r="C158">
@@ -2683,7 +2682,7 @@
       <c r="A159" s="1">
         <v>43296</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B159" t="s">
         <v>5</v>
       </c>
       <c r="C159">
@@ -2697,7 +2696,7 @@
       <c r="A160" s="1">
         <v>43296</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="B160" t="s">
         <v>5</v>
       </c>
       <c r="C160">
@@ -2711,7 +2710,7 @@
       <c r="A161" s="1">
         <v>43296</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="B161" t="s">
         <v>7</v>
       </c>
       <c r="C161">
@@ -2725,7 +2724,7 @@
       <c r="A162" s="1">
         <v>43296</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="B162" t="s">
         <v>8</v>
       </c>
       <c r="C162">
@@ -2739,7 +2738,7 @@
       <c r="A163" s="1">
         <v>43296</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B163" t="s">
         <v>4</v>
       </c>
       <c r="C163">
@@ -2753,7 +2752,7 @@
       <c r="A164" s="1">
         <v>43297</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="B164" t="s">
         <v>7</v>
       </c>
       <c r="C164">
@@ -2767,7 +2766,7 @@
       <c r="A165" s="1">
         <v>43297</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B165" t="s">
         <v>7</v>
       </c>
       <c r="C165">
@@ -2781,7 +2780,7 @@
       <c r="A166" s="1">
         <v>43297</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B166" t="s">
         <v>5</v>
       </c>
       <c r="C166">
@@ -2795,7 +2794,7 @@
       <c r="A167" s="1">
         <v>43297</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B167" t="s">
         <v>8</v>
       </c>
       <c r="C167">
@@ -2809,7 +2808,7 @@
       <c r="A168" s="1">
         <v>43297</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" t="s">
         <v>8</v>
       </c>
       <c r="C168">
@@ -2823,7 +2822,7 @@
       <c r="A169" s="1">
         <v>43297</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="B169" t="s">
         <v>8</v>
       </c>
       <c r="C169">
@@ -2837,7 +2836,7 @@
       <c r="A170" s="1">
         <v>43297</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="B170" t="s">
         <v>6</v>
       </c>
       <c r="C170">
@@ -2851,7 +2850,7 @@
       <c r="A171" s="1">
         <v>43297</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="B171" t="s">
         <v>8</v>
       </c>
       <c r="C171">
@@ -2865,7 +2864,7 @@
       <c r="A172" s="1">
         <v>43297</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="B172" t="s">
         <v>5</v>
       </c>
       <c r="C172">
@@ -2879,7 +2878,7 @@
       <c r="A173" s="1">
         <v>43297</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="B173" t="s">
         <v>5</v>
       </c>
       <c r="C173">
@@ -2893,7 +2892,7 @@
       <c r="A174" s="1">
         <v>43297</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="B174" t="s">
         <v>5</v>
       </c>
       <c r="C174">
@@ -2907,7 +2906,7 @@
       <c r="A175" s="1">
         <v>43298</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="B175" t="s">
         <v>6</v>
       </c>
       <c r="C175">
@@ -2921,7 +2920,7 @@
       <c r="A176" s="1">
         <v>43298</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="B176" t="s">
         <v>4</v>
       </c>
       <c r="C176">
@@ -2935,7 +2934,7 @@
       <c r="A177" s="1">
         <v>43298</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="B177" t="s">
         <v>7</v>
       </c>
       <c r="C177">
@@ -2949,7 +2948,7 @@
       <c r="A178" s="1">
         <v>43298</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="B178" t="s">
         <v>7</v>
       </c>
       <c r="C178">
@@ -2963,7 +2962,7 @@
       <c r="A179" s="1">
         <v>43298</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="B179" t="s">
         <v>5</v>
       </c>
       <c r="C179">
@@ -2977,7 +2976,7 @@
       <c r="A180" s="1">
         <v>43298</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="B180" t="s">
         <v>7</v>
       </c>
       <c r="C180">
@@ -2991,7 +2990,7 @@
       <c r="A181" s="1">
         <v>43298</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="B181" t="s">
         <v>4</v>
       </c>
       <c r="C181">
@@ -3005,7 +3004,7 @@
       <c r="A182" s="1">
         <v>43298</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="B182" t="s">
         <v>4</v>
       </c>
       <c r="C182">
@@ -3019,7 +3018,7 @@
       <c r="A183" s="1">
         <v>43298</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="B183" t="s">
         <v>4</v>
       </c>
       <c r="C183">
@@ -3033,7 +3032,7 @@
       <c r="A184" s="1">
         <v>43298</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="B184" t="s">
         <v>6</v>
       </c>
       <c r="C184">
@@ -3047,7 +3046,7 @@
       <c r="A185" s="1">
         <v>43298</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="B185" t="s">
         <v>8</v>
       </c>
       <c r="C185">
@@ -3061,7 +3060,7 @@
       <c r="A186" s="1">
         <v>43298</v>
       </c>
-      <c r="B186" s="2" t="s">
+      <c r="B186" t="s">
         <v>4</v>
       </c>
       <c r="C186">
@@ -3075,7 +3074,7 @@
       <c r="A187" s="1">
         <v>43298</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B187" t="s">
         <v>5</v>
       </c>
       <c r="C187">
@@ -3089,7 +3088,7 @@
       <c r="A188" s="1">
         <v>43299</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="B188" t="s">
         <v>6</v>
       </c>
       <c r="C188">
@@ -3103,7 +3102,7 @@
       <c r="A189" s="1">
         <v>43299</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B189" t="s">
         <v>4</v>
       </c>
       <c r="C189">
@@ -3117,7 +3116,7 @@
       <c r="A190" s="1">
         <v>43299</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B190" t="s">
         <v>5</v>
       </c>
       <c r="C190">
@@ -3131,7 +3130,7 @@
       <c r="A191" s="1">
         <v>43299</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="B191" t="s">
         <v>8</v>
       </c>
       <c r="C191">
@@ -3145,7 +3144,7 @@
       <c r="A192" s="1">
         <v>43299</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="B192" t="s">
         <v>7</v>
       </c>
       <c r="C192">
@@ -3159,7 +3158,7 @@
       <c r="A193" s="1">
         <v>43299</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="B193" t="s">
         <v>6</v>
       </c>
       <c r="C193">
@@ -3173,7 +3172,7 @@
       <c r="A194" s="1">
         <v>43299</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B194" t="s">
         <v>7</v>
       </c>
       <c r="C194">
@@ -3187,7 +3186,7 @@
       <c r="A195" s="1">
         <v>43299</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="B195" t="s">
         <v>6</v>
       </c>
       <c r="C195">
@@ -3201,7 +3200,7 @@
       <c r="A196" s="1">
         <v>43299</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="B196" t="s">
         <v>8</v>
       </c>
       <c r="C196">
@@ -3215,7 +3214,7 @@
       <c r="A197" s="1">
         <v>43299</v>
       </c>
-      <c r="B197" s="2" t="s">
+      <c r="B197" t="s">
         <v>7</v>
       </c>
       <c r="C197">
@@ -3229,7 +3228,7 @@
       <c r="A198" s="1">
         <v>43300</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B198" t="s">
         <v>4</v>
       </c>
       <c r="C198">
@@ -3243,7 +3242,7 @@
       <c r="A199" s="1">
         <v>43300</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B199" t="s">
         <v>8</v>
       </c>
       <c r="C199">
@@ -3257,7 +3256,7 @@
       <c r="A200" s="1">
         <v>43300</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="B200" t="s">
         <v>7</v>
       </c>
       <c r="C200">
@@ -3271,7 +3270,7 @@
       <c r="A201" s="1">
         <v>43300</v>
       </c>
-      <c r="B201" s="2" t="s">
+      <c r="B201" t="s">
         <v>6</v>
       </c>
       <c r="C201">
@@ -3285,7 +3284,7 @@
       <c r="A202" s="1">
         <v>43300</v>
       </c>
-      <c r="B202" s="2" t="s">
+      <c r="B202" t="s">
         <v>5</v>
       </c>
       <c r="C202">
@@ -3299,7 +3298,7 @@
       <c r="A203" s="1">
         <v>43300</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B203" t="s">
         <v>4</v>
       </c>
       <c r="C203">
@@ -3313,7 +3312,7 @@
       <c r="A204" s="1">
         <v>43300</v>
       </c>
-      <c r="B204" s="2" t="s">
+      <c r="B204" t="s">
         <v>7</v>
       </c>
       <c r="C204">
@@ -3327,7 +3326,7 @@
       <c r="A205" s="1">
         <v>43301</v>
       </c>
-      <c r="B205" s="2" t="s">
+      <c r="B205" t="s">
         <v>7</v>
       </c>
       <c r="C205">
@@ -3341,7 +3340,7 @@
       <c r="A206" s="1">
         <v>43301</v>
       </c>
-      <c r="B206" s="2" t="s">
+      <c r="B206" t="s">
         <v>8</v>
       </c>
       <c r="C206">
@@ -3355,7 +3354,7 @@
       <c r="A207" s="1">
         <v>43301</v>
       </c>
-      <c r="B207" s="2" t="s">
+      <c r="B207" t="s">
         <v>5</v>
       </c>
       <c r="C207">
@@ -3369,7 +3368,7 @@
       <c r="A208" s="1">
         <v>43301</v>
       </c>
-      <c r="B208" s="2" t="s">
+      <c r="B208" t="s">
         <v>8</v>
       </c>
       <c r="C208">
@@ -3383,7 +3382,7 @@
       <c r="A209" s="1">
         <v>43301</v>
       </c>
-      <c r="B209" s="2" t="s">
+      <c r="B209" t="s">
         <v>7</v>
       </c>
       <c r="C209">
@@ -3397,7 +3396,7 @@
       <c r="A210" s="1">
         <v>43301</v>
       </c>
-      <c r="B210" s="2" t="s">
+      <c r="B210" t="s">
         <v>7</v>
       </c>
       <c r="C210">
@@ -3411,7 +3410,7 @@
       <c r="A211" s="1">
         <v>43301</v>
       </c>
-      <c r="B211" s="2" t="s">
+      <c r="B211" t="s">
         <v>5</v>
       </c>
       <c r="C211">
@@ -3425,7 +3424,7 @@
       <c r="A212" s="1">
         <v>43302</v>
       </c>
-      <c r="B212" s="2" t="s">
+      <c r="B212" t="s">
         <v>8</v>
       </c>
       <c r="C212">
@@ -3439,7 +3438,7 @@
       <c r="A213" s="1">
         <v>43302</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="B213" t="s">
         <v>5</v>
       </c>
       <c r="C213">
@@ -3453,7 +3452,7 @@
       <c r="A214" s="1">
         <v>43302</v>
       </c>
-      <c r="B214" s="2" t="s">
+      <c r="B214" t="s">
         <v>8</v>
       </c>
       <c r="C214">
@@ -3467,7 +3466,7 @@
       <c r="A215" s="1">
         <v>43302</v>
       </c>
-      <c r="B215" s="2" t="s">
+      <c r="B215" t="s">
         <v>7</v>
       </c>
       <c r="C215">
@@ -3481,7 +3480,7 @@
       <c r="A216" s="1">
         <v>43302</v>
       </c>
-      <c r="B216" s="2" t="s">
+      <c r="B216" t="s">
         <v>5</v>
       </c>
       <c r="C216">
@@ -3495,7 +3494,7 @@
       <c r="A217" s="1">
         <v>43302</v>
       </c>
-      <c r="B217" s="2" t="s">
+      <c r="B217" t="s">
         <v>8</v>
       </c>
       <c r="C217">
@@ -3509,7 +3508,7 @@
       <c r="A218" s="1">
         <v>43302</v>
       </c>
-      <c r="B218" s="2" t="s">
+      <c r="B218" t="s">
         <v>6</v>
       </c>
       <c r="C218">
@@ -3523,7 +3522,7 @@
       <c r="A219" s="1">
         <v>43302</v>
       </c>
-      <c r="B219" s="2" t="s">
+      <c r="B219" t="s">
         <v>5</v>
       </c>
       <c r="C219">
@@ -3537,7 +3536,7 @@
       <c r="A220" s="1">
         <v>43302</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="B220" t="s">
         <v>4</v>
       </c>
       <c r="C220">
@@ -3551,7 +3550,7 @@
       <c r="A221" s="1">
         <v>43302</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="B221" t="s">
         <v>6</v>
       </c>
       <c r="C221">
@@ -3565,7 +3564,7 @@
       <c r="A222" s="1">
         <v>43302</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="B222" t="s">
         <v>4</v>
       </c>
       <c r="C222">
@@ -3579,7 +3578,7 @@
       <c r="A223" s="1">
         <v>43302</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="B223" t="s">
         <v>8</v>
       </c>
       <c r="C223">
@@ -3593,7 +3592,7 @@
       <c r="A224" s="1">
         <v>43302</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="B224" t="s">
         <v>6</v>
       </c>
       <c r="C224">
@@ -3607,7 +3606,7 @@
       <c r="A225" s="1">
         <v>43303</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="B225" t="s">
         <v>6</v>
       </c>
       <c r="C225">
@@ -3621,7 +3620,7 @@
       <c r="A226" s="1">
         <v>43303</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="B226" t="s">
         <v>7</v>
       </c>
       <c r="C226">
@@ -3635,7 +3634,7 @@
       <c r="A227" s="1">
         <v>43303</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="B227" t="s">
         <v>4</v>
       </c>
       <c r="C227">
@@ -3649,7 +3648,7 @@
       <c r="A228" s="1">
         <v>43303</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="B228" t="s">
         <v>5</v>
       </c>
       <c r="C228">
@@ -3663,7 +3662,7 @@
       <c r="A229" s="1">
         <v>43303</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="B229" t="s">
         <v>7</v>
       </c>
       <c r="C229">
@@ -3677,7 +3676,7 @@
       <c r="A230" s="1">
         <v>43303</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="B230" t="s">
         <v>8</v>
       </c>
       <c r="C230">
@@ -3691,7 +3690,7 @@
       <c r="A231" s="1">
         <v>43303</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="B231" t="s">
         <v>6</v>
       </c>
       <c r="C231">
@@ -3705,7 +3704,7 @@
       <c r="A232" s="1">
         <v>43303</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="B232" t="s">
         <v>7</v>
       </c>
       <c r="C232">
@@ -3719,7 +3718,7 @@
       <c r="A233" s="1">
         <v>43303</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="B233" t="s">
         <v>8</v>
       </c>
       <c r="C233">
@@ -3733,7 +3732,7 @@
       <c r="A234" s="1">
         <v>43303</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="B234" t="s">
         <v>8</v>
       </c>
       <c r="C234">
@@ -3747,7 +3746,7 @@
       <c r="A235" s="1">
         <v>43303</v>
       </c>
-      <c r="B235" s="2" t="s">
+      <c r="B235" t="s">
         <v>8</v>
       </c>
       <c r="C235">
@@ -3761,7 +3760,7 @@
       <c r="A236" s="1">
         <v>43303</v>
       </c>
-      <c r="B236" s="2" t="s">
+      <c r="B236" t="s">
         <v>4</v>
       </c>
       <c r="C236">
@@ -3775,7 +3774,7 @@
       <c r="A237" s="1">
         <v>43303</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="B237" t="s">
         <v>5</v>
       </c>
       <c r="C237">
@@ -3789,7 +3788,7 @@
       <c r="A238" s="1">
         <v>43303</v>
       </c>
-      <c r="B238" s="2" t="s">
+      <c r="B238" t="s">
         <v>8</v>
       </c>
       <c r="C238">
@@ -3803,7 +3802,7 @@
       <c r="A239" s="1">
         <v>43304</v>
       </c>
-      <c r="B239" s="2" t="s">
+      <c r="B239" t="s">
         <v>7</v>
       </c>
       <c r="C239">
@@ -3817,7 +3816,7 @@
       <c r="A240" s="1">
         <v>43304</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="B240" t="s">
         <v>4</v>
       </c>
       <c r="C240">
@@ -3831,7 +3830,7 @@
       <c r="A241" s="1">
         <v>43304</v>
       </c>
-      <c r="B241" s="2" t="s">
+      <c r="B241" t="s">
         <v>5</v>
       </c>
       <c r="C241">
@@ -3845,7 +3844,7 @@
       <c r="A242" s="1">
         <v>43304</v>
       </c>
-      <c r="B242" s="2" t="s">
+      <c r="B242" t="s">
         <v>7</v>
       </c>
       <c r="C242">
@@ -3859,7 +3858,7 @@
       <c r="A243" s="1">
         <v>43304</v>
       </c>
-      <c r="B243" s="2" t="s">
+      <c r="B243" t="s">
         <v>7</v>
       </c>
       <c r="C243">
@@ -3873,7 +3872,7 @@
       <c r="A244" s="1">
         <v>43304</v>
       </c>
-      <c r="B244" s="2" t="s">
+      <c r="B244" t="s">
         <v>6</v>
       </c>
       <c r="C244">
@@ -3887,7 +3886,7 @@
       <c r="A245" s="1">
         <v>43304</v>
       </c>
-      <c r="B245" s="2" t="s">
+      <c r="B245" t="s">
         <v>6</v>
       </c>
       <c r="C245">
@@ -3901,7 +3900,7 @@
       <c r="A246" s="1">
         <v>43304</v>
       </c>
-      <c r="B246" s="2" t="s">
+      <c r="B246" t="s">
         <v>6</v>
       </c>
       <c r="C246">
@@ -3915,7 +3914,7 @@
       <c r="A247" s="1">
         <v>43304</v>
       </c>
-      <c r="B247" s="2" t="s">
+      <c r="B247" t="s">
         <v>5</v>
       </c>
       <c r="C247">
@@ -3929,7 +3928,7 @@
       <c r="A248" s="1">
         <v>43304</v>
       </c>
-      <c r="B248" s="2" t="s">
+      <c r="B248" t="s">
         <v>6</v>
       </c>
       <c r="C248">
@@ -3943,7 +3942,7 @@
       <c r="A249" s="1">
         <v>43304</v>
       </c>
-      <c r="B249" s="2" t="s">
+      <c r="B249" t="s">
         <v>8</v>
       </c>
       <c r="C249">
@@ -3957,7 +3956,7 @@
       <c r="A250" s="1">
         <v>43305</v>
       </c>
-      <c r="B250" s="2" t="s">
+      <c r="B250" t="s">
         <v>8</v>
       </c>
       <c r="C250">
@@ -3971,7 +3970,7 @@
       <c r="A251" s="1">
         <v>43305</v>
       </c>
-      <c r="B251" s="2" t="s">
+      <c r="B251" t="s">
         <v>6</v>
       </c>
       <c r="C251">
@@ -3985,7 +3984,7 @@
       <c r="A252" s="1">
         <v>43305</v>
       </c>
-      <c r="B252" s="2" t="s">
+      <c r="B252" t="s">
         <v>4</v>
       </c>
       <c r="C252">
@@ -3999,7 +3998,7 @@
       <c r="A253" s="1">
         <v>43305</v>
       </c>
-      <c r="B253" s="2" t="s">
+      <c r="B253" t="s">
         <v>7</v>
       </c>
       <c r="C253">
@@ -4013,7 +4012,7 @@
       <c r="A254" s="1">
         <v>43305</v>
       </c>
-      <c r="B254" s="2" t="s">
+      <c r="B254" t="s">
         <v>6</v>
       </c>
       <c r="C254">
@@ -4027,7 +4026,7 @@
       <c r="A255" s="1">
         <v>43305</v>
       </c>
-      <c r="B255" s="2" t="s">
+      <c r="B255" t="s">
         <v>5</v>
       </c>
       <c r="C255">
@@ -4041,7 +4040,7 @@
       <c r="A256" s="1">
         <v>43305</v>
       </c>
-      <c r="B256" s="2" t="s">
+      <c r="B256" t="s">
         <v>4</v>
       </c>
       <c r="C256">
@@ -4055,7 +4054,7 @@
       <c r="A257" s="1">
         <v>43305</v>
       </c>
-      <c r="B257" s="2" t="s">
+      <c r="B257" t="s">
         <v>8</v>
       </c>
       <c r="C257">
@@ -4069,7 +4068,7 @@
       <c r="A258" s="1">
         <v>43305</v>
       </c>
-      <c r="B258" s="2" t="s">
+      <c r="B258" t="s">
         <v>5</v>
       </c>
       <c r="C258">
@@ -4083,7 +4082,7 @@
       <c r="A259" s="1">
         <v>43305</v>
       </c>
-      <c r="B259" s="2" t="s">
+      <c r="B259" t="s">
         <v>5</v>
       </c>
       <c r="C259">
@@ -4097,7 +4096,7 @@
       <c r="A260" s="1">
         <v>43305</v>
       </c>
-      <c r="B260" s="2" t="s">
+      <c r="B260" t="s">
         <v>8</v>
       </c>
       <c r="C260">
@@ -4111,7 +4110,7 @@
       <c r="A261" s="1">
         <v>43305</v>
       </c>
-      <c r="B261" s="2" t="s">
+      <c r="B261" t="s">
         <v>5</v>
       </c>
       <c r="C261">
@@ -4125,7 +4124,7 @@
       <c r="A262" s="1">
         <v>43305</v>
       </c>
-      <c r="B262" s="2" t="s">
+      <c r="B262" t="s">
         <v>8</v>
       </c>
       <c r="C262">
@@ -4139,7 +4138,7 @@
       <c r="A263" s="1">
         <v>43305</v>
       </c>
-      <c r="B263" s="2" t="s">
+      <c r="B263" t="s">
         <v>7</v>
       </c>
       <c r="C263">
@@ -4153,7 +4152,7 @@
       <c r="A264" s="1">
         <v>43306</v>
       </c>
-      <c r="B264" s="2" t="s">
+      <c r="B264" t="s">
         <v>8</v>
       </c>
       <c r="C264">
@@ -4167,7 +4166,7 @@
       <c r="A265" s="1">
         <v>43306</v>
       </c>
-      <c r="B265" s="2" t="s">
+      <c r="B265" t="s">
         <v>4</v>
       </c>
       <c r="C265">
@@ -4181,7 +4180,7 @@
       <c r="A266" s="1">
         <v>43306</v>
       </c>
-      <c r="B266" s="2" t="s">
+      <c r="B266" t="s">
         <v>5</v>
       </c>
       <c r="C266">
@@ -4195,7 +4194,7 @@
       <c r="A267" s="1">
         <v>43306</v>
       </c>
-      <c r="B267" s="2" t="s">
+      <c r="B267" t="s">
         <v>5</v>
       </c>
       <c r="C267">
@@ -4209,7 +4208,7 @@
       <c r="A268" s="1">
         <v>43306</v>
       </c>
-      <c r="B268" s="2" t="s">
+      <c r="B268" t="s">
         <v>7</v>
       </c>
       <c r="C268">
@@ -4223,7 +4222,7 @@
       <c r="A269" s="1">
         <v>43306</v>
       </c>
-      <c r="B269" s="2" t="s">
+      <c r="B269" t="s">
         <v>5</v>
       </c>
       <c r="C269">
@@ -4237,7 +4236,7 @@
       <c r="A270" s="1">
         <v>43306</v>
       </c>
-      <c r="B270" s="2" t="s">
+      <c r="B270" t="s">
         <v>5</v>
       </c>
       <c r="C270">
@@ -4251,7 +4250,7 @@
       <c r="A271" s="1">
         <v>43306</v>
       </c>
-      <c r="B271" s="2" t="s">
+      <c r="B271" t="s">
         <v>7</v>
       </c>
       <c r="C271">
@@ -4265,7 +4264,7 @@
       <c r="A272" s="1">
         <v>43306</v>
       </c>
-      <c r="B272" s="2" t="s">
+      <c r="B272" t="s">
         <v>5</v>
       </c>
       <c r="C272">
@@ -4279,7 +4278,7 @@
       <c r="A273" s="1">
         <v>43306</v>
       </c>
-      <c r="B273" s="2" t="s">
+      <c r="B273" t="s">
         <v>4</v>
       </c>
       <c r="C273">
@@ -4293,7 +4292,7 @@
       <c r="A274" s="1">
         <v>43306</v>
       </c>
-      <c r="B274" s="2" t="s">
+      <c r="B274" t="s">
         <v>8</v>
       </c>
       <c r="C274">
@@ -4307,7 +4306,7 @@
       <c r="A275" s="1">
         <v>43306</v>
       </c>
-      <c r="B275" s="2" t="s">
+      <c r="B275" t="s">
         <v>6</v>
       </c>
       <c r="C275">
@@ -4321,7 +4320,7 @@
       <c r="A276" s="1">
         <v>43306</v>
       </c>
-      <c r="B276" s="2" t="s">
+      <c r="B276" t="s">
         <v>6</v>
       </c>
       <c r="C276">
@@ -4335,7 +4334,7 @@
       <c r="A277" s="1">
         <v>43306</v>
       </c>
-      <c r="B277" s="2" t="s">
+      <c r="B277" t="s">
         <v>6</v>
       </c>
       <c r="C277">
@@ -4349,7 +4348,7 @@
       <c r="A278" s="1">
         <v>43306</v>
       </c>
-      <c r="B278" s="2" t="s">
+      <c r="B278" t="s">
         <v>6</v>
       </c>
       <c r="C278">
@@ -4363,7 +4362,7 @@
       <c r="A279" s="1">
         <v>43306</v>
       </c>
-      <c r="B279" s="2" t="s">
+      <c r="B279" t="s">
         <v>6</v>
       </c>
       <c r="C279">
@@ -4377,7 +4376,7 @@
       <c r="A280" s="1">
         <v>43306</v>
       </c>
-      <c r="B280" s="2" t="s">
+      <c r="B280" t="s">
         <v>4</v>
       </c>
       <c r="C280">
@@ -4391,7 +4390,7 @@
       <c r="A281" s="1">
         <v>43306</v>
       </c>
-      <c r="B281" s="2" t="s">
+      <c r="B281" t="s">
         <v>4</v>
       </c>
       <c r="C281">
@@ -4405,7 +4404,7 @@
       <c r="A282" s="1">
         <v>43307</v>
       </c>
-      <c r="B282" s="2" t="s">
+      <c r="B282" t="s">
         <v>8</v>
       </c>
       <c r="C282">
@@ -4419,7 +4418,7 @@
       <c r="A283" s="1">
         <v>43307</v>
       </c>
-      <c r="B283" s="2" t="s">
+      <c r="B283" t="s">
         <v>4</v>
       </c>
       <c r="C283">
@@ -4433,7 +4432,7 @@
       <c r="A284" s="1">
         <v>43307</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="B284" t="s">
         <v>6</v>
       </c>
       <c r="C284">
@@ -4447,7 +4446,7 @@
       <c r="A285" s="1">
         <v>43307</v>
       </c>
-      <c r="B285" s="2" t="s">
+      <c r="B285" t="s">
         <v>5</v>
       </c>
       <c r="C285">
@@ -4461,7 +4460,7 @@
       <c r="A286" s="1">
         <v>43307</v>
       </c>
-      <c r="B286" s="2" t="s">
+      <c r="B286" t="s">
         <v>5</v>
       </c>
       <c r="C286">
@@ -4475,7 +4474,7 @@
       <c r="A287" s="1">
         <v>43307</v>
       </c>
-      <c r="B287" s="2" t="s">
+      <c r="B287" t="s">
         <v>4</v>
       </c>
       <c r="C287">
@@ -4489,7 +4488,7 @@
       <c r="A288" s="1">
         <v>43307</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="B288" t="s">
         <v>6</v>
       </c>
       <c r="C288">
@@ -4503,7 +4502,7 @@
       <c r="A289" s="1">
         <v>43307</v>
       </c>
-      <c r="B289" s="2" t="s">
+      <c r="B289" t="s">
         <v>8</v>
       </c>
       <c r="C289">
@@ -4517,7 +4516,7 @@
       <c r="A290" s="1">
         <v>43307</v>
       </c>
-      <c r="B290" s="2" t="s">
+      <c r="B290" t="s">
         <v>8</v>
       </c>
       <c r="C290">
@@ -4531,7 +4530,7 @@
       <c r="A291" s="1">
         <v>43307</v>
       </c>
-      <c r="B291" s="2" t="s">
+      <c r="B291" t="s">
         <v>6</v>
       </c>
       <c r="C291">
@@ -4545,7 +4544,7 @@
       <c r="A292" s="1">
         <v>43307</v>
       </c>
-      <c r="B292" s="2" t="s">
+      <c r="B292" t="s">
         <v>4</v>
       </c>
       <c r="C292">
@@ -4559,7 +4558,7 @@
       <c r="A293" s="1">
         <v>43308</v>
       </c>
-      <c r="B293" s="2" t="s">
+      <c r="B293" t="s">
         <v>4</v>
       </c>
       <c r="C293">
@@ -4573,7 +4572,7 @@
       <c r="A294" s="1">
         <v>43308</v>
       </c>
-      <c r="B294" s="2" t="s">
+      <c r="B294" t="s">
         <v>6</v>
       </c>
       <c r="C294">
@@ -4587,7 +4586,7 @@
       <c r="A295" s="1">
         <v>43308</v>
       </c>
-      <c r="B295" s="2" t="s">
+      <c r="B295" t="s">
         <v>7</v>
       </c>
       <c r="C295">
@@ -4601,7 +4600,7 @@
       <c r="A296" s="1">
         <v>43308</v>
       </c>
-      <c r="B296" s="2" t="s">
+      <c r="B296" t="s">
         <v>6</v>
       </c>
       <c r="C296">
@@ -4615,7 +4614,7 @@
       <c r="A297" s="1">
         <v>43308</v>
       </c>
-      <c r="B297" s="2" t="s">
+      <c r="B297" t="s">
         <v>5</v>
       </c>
       <c r="C297">
@@ -4629,7 +4628,7 @@
       <c r="A298" s="1">
         <v>43308</v>
       </c>
-      <c r="B298" s="2" t="s">
+      <c r="B298" t="s">
         <v>5</v>
       </c>
       <c r="C298">
@@ -4643,7 +4642,7 @@
       <c r="A299" s="1">
         <v>43308</v>
       </c>
-      <c r="B299" s="2" t="s">
+      <c r="B299" t="s">
         <v>8</v>
       </c>
       <c r="C299">
@@ -4657,7 +4656,7 @@
       <c r="A300" s="1">
         <v>43308</v>
       </c>
-      <c r="B300" s="2" t="s">
+      <c r="B300" t="s">
         <v>7</v>
       </c>
       <c r="C300">
@@ -4671,7 +4670,7 @@
       <c r="A301" s="1">
         <v>43309</v>
       </c>
-      <c r="B301" s="2" t="s">
+      <c r="B301" t="s">
         <v>4</v>
       </c>
       <c r="C301">
@@ -4685,7 +4684,7 @@
       <c r="A302" s="1">
         <v>43309</v>
       </c>
-      <c r="B302" s="2" t="s">
+      <c r="B302" t="s">
         <v>8</v>
       </c>
       <c r="C302">
@@ -4699,7 +4698,7 @@
       <c r="A303" s="1">
         <v>43309</v>
       </c>
-      <c r="B303" s="2" t="s">
+      <c r="B303" t="s">
         <v>4</v>
       </c>
       <c r="C303">
@@ -4713,7 +4712,7 @@
       <c r="A304" s="1">
         <v>43309</v>
       </c>
-      <c r="B304" s="2" t="s">
+      <c r="B304" t="s">
         <v>5</v>
       </c>
       <c r="C304">
@@ -4727,7 +4726,7 @@
       <c r="A305" s="1">
         <v>43309</v>
       </c>
-      <c r="B305" s="2" t="s">
+      <c r="B305" t="s">
         <v>6</v>
       </c>
       <c r="C305">
@@ -4741,7 +4740,7 @@
       <c r="A306" s="1">
         <v>43309</v>
       </c>
-      <c r="B306" s="2" t="s">
+      <c r="B306" t="s">
         <v>5</v>
       </c>
       <c r="C306">
@@ -4755,7 +4754,7 @@
       <c r="A307" s="1">
         <v>43309</v>
       </c>
-      <c r="B307" s="2" t="s">
+      <c r="B307" t="s">
         <v>8</v>
       </c>
       <c r="C307">
@@ -4769,7 +4768,7 @@
       <c r="A308" s="1">
         <v>43309</v>
       </c>
-      <c r="B308" s="2" t="s">
+      <c r="B308" t="s">
         <v>7</v>
       </c>
       <c r="C308">
@@ -4783,7 +4782,7 @@
       <c r="A309" s="1">
         <v>43309</v>
       </c>
-      <c r="B309" s="2" t="s">
+      <c r="B309" t="s">
         <v>4</v>
       </c>
       <c r="C309">
@@ -4797,7 +4796,7 @@
       <c r="A310" s="1">
         <v>43310</v>
       </c>
-      <c r="B310" s="2" t="s">
+      <c r="B310" t="s">
         <v>5</v>
       </c>
       <c r="C310">
@@ -4811,7 +4810,7 @@
       <c r="A311" s="1">
         <v>43310</v>
       </c>
-      <c r="B311" s="2" t="s">
+      <c r="B311" t="s">
         <v>6</v>
       </c>
       <c r="C311">
@@ -4825,7 +4824,7 @@
       <c r="A312" s="1">
         <v>43310</v>
       </c>
-      <c r="B312" s="2" t="s">
+      <c r="B312" t="s">
         <v>7</v>
       </c>
       <c r="C312">
@@ -4839,7 +4838,7 @@
       <c r="A313" s="1">
         <v>43310</v>
       </c>
-      <c r="B313" s="2" t="s">
+      <c r="B313" t="s">
         <v>4</v>
       </c>
       <c r="C313">
@@ -4853,7 +4852,7 @@
       <c r="A314" s="1">
         <v>43310</v>
       </c>
-      <c r="B314" s="2" t="s">
+      <c r="B314" t="s">
         <v>4</v>
       </c>
       <c r="C314">
@@ -4867,7 +4866,7 @@
       <c r="A315" s="1">
         <v>43310</v>
       </c>
-      <c r="B315" s="2" t="s">
+      <c r="B315" t="s">
         <v>4</v>
       </c>
       <c r="C315">
@@ -4881,7 +4880,7 @@
       <c r="A316" s="1">
         <v>43310</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="B316" t="s">
         <v>8</v>
       </c>
       <c r="C316">
@@ -4895,7 +4894,7 @@
       <c r="A317" s="1">
         <v>43311</v>
       </c>
-      <c r="B317" s="2" t="s">
+      <c r="B317" t="s">
         <v>8</v>
       </c>
       <c r="C317">
@@ -4909,7 +4908,7 @@
       <c r="A318" s="1">
         <v>43311</v>
       </c>
-      <c r="B318" s="2" t="s">
+      <c r="B318" t="s">
         <v>6</v>
       </c>
       <c r="C318">
@@ -4923,7 +4922,7 @@
       <c r="A319" s="1">
         <v>43311</v>
       </c>
-      <c r="B319" s="2" t="s">
+      <c r="B319" t="s">
         <v>5</v>
       </c>
       <c r="C319">
@@ -4937,7 +4936,7 @@
       <c r="A320" s="1">
         <v>43311</v>
       </c>
-      <c r="B320" s="2" t="s">
+      <c r="B320" t="s">
         <v>5</v>
       </c>
       <c r="C320">
@@ -4951,7 +4950,7 @@
       <c r="A321" s="1">
         <v>43311</v>
       </c>
-      <c r="B321" s="2" t="s">
+      <c r="B321" t="s">
         <v>7</v>
       </c>
       <c r="C321">
@@ -4965,7 +4964,7 @@
       <c r="A322" s="1">
         <v>43311</v>
       </c>
-      <c r="B322" s="2" t="s">
+      <c r="B322" t="s">
         <v>5</v>
       </c>
       <c r="C322">
@@ -4979,7 +4978,7 @@
       <c r="A323" s="1">
         <v>43311</v>
       </c>
-      <c r="B323" s="2" t="s">
+      <c r="B323" t="s">
         <v>6</v>
       </c>
       <c r="C323">
@@ -4993,7 +4992,7 @@
       <c r="A324" s="1">
         <v>43311</v>
       </c>
-      <c r="B324" s="2" t="s">
+      <c r="B324" t="s">
         <v>4</v>
       </c>
       <c r="C324">
@@ -5007,7 +5006,7 @@
       <c r="A325" s="1">
         <v>43311</v>
       </c>
-      <c r="B325" s="2" t="s">
+      <c r="B325" t="s">
         <v>4</v>
       </c>
       <c r="C325">
